--- a/data/odds/Campers and Skiers and Prahlad 2026 Betting Odds.xlsx
+++ b/data/odds/Campers and Skiers and Prahlad 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
   <si>
     <t>Record</t>
   </si>
@@ -30,130 +30,130 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Robbie's Rowdy Team</t>
+  </si>
+  <si>
     <t>Alley Cats</t>
   </si>
   <si>
+    <t>Maulin's Monstrous Team</t>
+  </si>
+  <si>
+    <t>The Turbanator</t>
+  </si>
+  <si>
+    <t>BB-Ate My Lemons</t>
+  </si>
+  <si>
     <t>Potato Squad</t>
   </si>
   <si>
     <t>Cutlet Slutz</t>
   </si>
   <si>
-    <t>Maulin's Monstrous Team</t>
-  </si>
-  <si>
-    <t>Robbie's Rowdy Team</t>
-  </si>
-  <si>
-    <t>The Turbanator</t>
-  </si>
-  <si>
-    <t>BB-Ate My Lemons</t>
-  </si>
-  <si>
     <t>Knee Chubbs</t>
   </si>
   <si>
+    <t>Michael the International Baker</t>
+  </si>
+  <si>
     <t>J.K. Dobby</t>
   </si>
   <si>
-    <t>Michael the International Baker</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>98.3%</t>
-  </si>
-  <si>
-    <t>90.2%</t>
-  </si>
-  <si>
-    <t>86.8%</t>
-  </si>
-  <si>
-    <t>85.3%</t>
-  </si>
-  <si>
-    <t>80.8%</t>
-  </si>
-  <si>
-    <t>70.7%</t>
-  </si>
-  <si>
-    <t>32.9%</t>
-  </si>
-  <si>
-    <t>30.7%</t>
-  </si>
-  <si>
-    <t>14.9%</t>
-  </si>
-  <si>
-    <t>9.4%</t>
-  </si>
-  <si>
-    <t>-5782</t>
-  </si>
-  <si>
-    <t>-920</t>
-  </si>
-  <si>
-    <t>-658</t>
-  </si>
-  <si>
-    <t>-580</t>
-  </si>
-  <si>
-    <t>-421</t>
-  </si>
-  <si>
-    <t>-241</t>
-  </si>
-  <si>
-    <t>+204</t>
-  </si>
-  <si>
-    <t>+226</t>
-  </si>
-  <si>
-    <t>+571</t>
-  </si>
-  <si>
-    <t>+964</t>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>99.4%</t>
+  </si>
+  <si>
+    <t>98.8%</t>
+  </si>
+  <si>
+    <t>94.4%</t>
+  </si>
+  <si>
+    <t>76.8%</t>
+  </si>
+  <si>
+    <t>72.2%</t>
+  </si>
+  <si>
+    <t>69.6%</t>
+  </si>
+  <si>
+    <t>58.1%</t>
+  </si>
+  <si>
+    <t>29.7%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>-16567</t>
+  </si>
+  <si>
+    <t>-8233</t>
+  </si>
+  <si>
+    <t>-1686</t>
+  </si>
+  <si>
+    <t>-331</t>
+  </si>
+  <si>
+    <t>-260</t>
+  </si>
+  <si>
+    <t>-229</t>
+  </si>
+  <si>
+    <t>-139</t>
+  </si>
+  <si>
+    <t>+237</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>50.0%</t>
-  </si>
-  <si>
-    <t>12.4%</t>
-  </si>
-  <si>
-    <t>11.8%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>10.0%</t>
-  </si>
-  <si>
-    <t>4.5%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
+    <t>48.2%</t>
+  </si>
+  <si>
+    <t>29.9%</t>
+  </si>
+  <si>
+    <t>15.3%</t>
+  </si>
+  <si>
+    <t>2.8%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
   </si>
   <si>
     <t>0.1%</t>
@@ -162,70 +162,58 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-100</t>
-  </si>
-  <si>
-    <t>+706</t>
-  </si>
-  <si>
-    <t>+747</t>
-  </si>
-  <si>
-    <t>+871</t>
-  </si>
-  <si>
-    <t>+900</t>
-  </si>
-  <si>
-    <t>+2122</t>
-  </si>
-  <si>
-    <t>+19900</t>
-  </si>
-  <si>
-    <t>+24900</t>
+    <t>+107</t>
+  </si>
+  <si>
+    <t>+234</t>
+  </si>
+  <si>
+    <t>+554</t>
+  </si>
+  <si>
+    <t>+3471</t>
+  </si>
+  <si>
+    <t>+6567</t>
+  </si>
+  <si>
+    <t>+8233</t>
+  </si>
+  <si>
+    <t>+9900</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>+∞</t>
-  </si>
-  <si>
-    <t>40.9%</t>
-  </si>
-  <si>
-    <t>28.9%</t>
-  </si>
-  <si>
-    <t>16.0%</t>
-  </si>
-  <si>
-    <t>8.8%</t>
-  </si>
-  <si>
-    <t>3.1%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>+144</t>
-  </si>
-  <si>
-    <t>+246</t>
-  </si>
-  <si>
-    <t>+525</t>
-  </si>
-  <si>
-    <t>+1036</t>
-  </si>
-  <si>
-    <t>+3126</t>
-  </si>
-  <si>
-    <t>+9900</t>
+    <t>64.3%</t>
+  </si>
+  <si>
+    <t>33.7%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>-180</t>
+  </si>
+  <si>
+    <t>+197</t>
+  </si>
+  <si>
+    <t>+7043</t>
+  </si>
+  <si>
+    <t>+33233</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -608,10 +596,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -619,13 +607,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -633,13 +621,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -647,13 +635,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -664,10 +652,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -675,13 +663,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -692,10 +680,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -703,13 +691,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -717,13 +705,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -731,13 +719,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -772,7 +760,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>48</v>
@@ -780,13 +768,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>49</v>
@@ -794,13 +782,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>50</v>
@@ -808,13 +796,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
@@ -822,13 +810,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>52</v>
@@ -839,10 +827,10 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>53</v>
@@ -856,7 +844,7 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>54</v>
@@ -867,10 +855,10 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
         <v>55</v>
@@ -881,13 +869,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -895,13 +883,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
         <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -922,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -933,13 +921,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -947,13 +935,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -961,13 +949,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -978,10 +966,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -989,13 +977,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1006,35 +994,35 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
         <v>55</v>
@@ -1042,13 +1030,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
         <v>55</v>
@@ -1056,7 +1044,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1065,7 +1053,7 @@
         <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Campers and Skiers and Prahlad 2026 Betting Odds.xlsx
+++ b/data/odds/Campers and Skiers and Prahlad 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="71">
   <si>
     <t>Record</t>
   </si>
@@ -39,181 +39,196 @@
     <t>Maulin's Monstrous Team</t>
   </si>
   <si>
+    <t>Potato Squad</t>
+  </si>
+  <si>
+    <t>BB-Ate My Lemons</t>
+  </si>
+  <si>
     <t>The Turbanator</t>
   </si>
   <si>
-    <t>BB-Ate My Lemons</t>
-  </si>
-  <si>
-    <t>Potato Squad</t>
-  </si>
-  <si>
     <t>Cutlet Slutz</t>
   </si>
   <si>
+    <t>J.K. Dobby</t>
+  </si>
+  <si>
+    <t>LaPortAuthority</t>
+  </si>
+  <si>
     <t>Knee Chubbs</t>
   </si>
   <si>
-    <t>Michael the International Baker</t>
-  </si>
-  <si>
-    <t>J.K. Dobby</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>99.4%</t>
-  </si>
-  <si>
-    <t>98.8%</t>
-  </si>
-  <si>
-    <t>94.4%</t>
-  </si>
-  <si>
-    <t>76.8%</t>
-  </si>
-  <si>
-    <t>72.2%</t>
-  </si>
-  <si>
-    <t>69.6%</t>
-  </si>
-  <si>
-    <t>58.1%</t>
-  </si>
-  <si>
-    <t>29.7%</t>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>99.7%</t>
+  </si>
+  <si>
+    <t>96.2%</t>
+  </si>
+  <si>
+    <t>88.7%</t>
+  </si>
+  <si>
+    <t>87.3%</t>
+  </si>
+  <si>
+    <t>81.6%</t>
+  </si>
+  <si>
+    <t>63.4%</t>
+  </si>
+  <si>
+    <t>29.9%</t>
+  </si>
+  <si>
+    <t>21.7%</t>
+  </si>
+  <si>
+    <t>21.2%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
+  </si>
+  <si>
+    <t>-33233</t>
+  </si>
+  <si>
+    <t>-2532</t>
+  </si>
+  <si>
+    <t>-785</t>
+  </si>
+  <si>
+    <t>-687</t>
+  </si>
+  <si>
+    <t>-443</t>
+  </si>
+  <si>
+    <t>-173</t>
+  </si>
+  <si>
+    <t>+234</t>
+  </si>
+  <si>
+    <t>+361</t>
+  </si>
+  <si>
+    <t>+372</t>
+  </si>
+  <si>
+    <t>+871</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>67.0%</t>
+  </si>
+  <si>
+    <t>16.4%</t>
+  </si>
+  <si>
+    <t>7.2%</t>
+  </si>
+  <si>
+    <t>4.8%</t>
+  </si>
+  <si>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-203</t>
+  </si>
+  <si>
+    <t>+510</t>
+  </si>
+  <si>
+    <t>+1289</t>
+  </si>
+  <si>
+    <t>+1983</t>
+  </si>
+  <si>
+    <t>+2930</t>
+  </si>
+  <si>
+    <t>+9900</t>
+  </si>
+  <si>
+    <t>+49900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>38.8%</t>
+  </si>
+  <si>
+    <t>21.0%</t>
+  </si>
+  <si>
+    <t>20.3%</t>
+  </si>
+  <si>
+    <t>14.4%</t>
+  </si>
+  <si>
+    <t>2.9%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
   </si>
   <si>
     <t>0.6%</t>
   </si>
   <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>-16567</t>
-  </si>
-  <si>
-    <t>-8233</t>
-  </si>
-  <si>
-    <t>-1686</t>
-  </si>
-  <si>
-    <t>-331</t>
-  </si>
-  <si>
-    <t>-260</t>
-  </si>
-  <si>
-    <t>-229</t>
-  </si>
-  <si>
-    <t>-139</t>
-  </si>
-  <si>
-    <t>+237</t>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>+158</t>
+  </si>
+  <si>
+    <t>+376</t>
+  </si>
+  <si>
+    <t>+393</t>
+  </si>
+  <si>
+    <t>+594</t>
+  </si>
+  <si>
+    <t>+3348</t>
+  </si>
+  <si>
+    <t>+6567</t>
   </si>
   <si>
     <t>+16567</t>
   </si>
   <si>
-    <t>+24900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>48.2%</t>
-  </si>
-  <si>
-    <t>29.9%</t>
-  </si>
-  <si>
-    <t>15.3%</t>
-  </si>
-  <si>
-    <t>2.8%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>+107</t>
-  </si>
-  <si>
-    <t>+234</t>
-  </si>
-  <si>
-    <t>+554</t>
-  </si>
-  <si>
-    <t>+3471</t>
-  </si>
-  <si>
-    <t>+6567</t>
-  </si>
-  <si>
-    <t>+8233</t>
-  </si>
-  <si>
-    <t>+9900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>64.3%</t>
-  </si>
-  <si>
-    <t>33.7%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>-180</t>
-  </si>
-  <si>
-    <t>+197</t>
-  </si>
-  <si>
-    <t>+7043</t>
-  </si>
-  <si>
     <t>+33233</t>
-  </si>
-  <si>
-    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -596,10 +611,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -610,10 +625,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -621,13 +636,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -635,13 +650,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -649,13 +664,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -666,10 +681,10 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -677,13 +692,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -694,10 +709,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -705,13 +720,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -719,13 +734,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -746,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -760,10 +775,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -774,10 +789,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -785,13 +800,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -799,13 +814,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -813,13 +828,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -830,10 +845,10 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -841,13 +856,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -858,10 +873,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -869,13 +884,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -883,13 +898,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -910,7 +925,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -921,41 +936,41 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -963,13 +978,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -980,10 +995,10 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -991,69 +1006,69 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Campers and Skiers and Prahlad 2026 Betting Odds.xlsx
+++ b/data/odds/Campers and Skiers and Prahlad 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
   <si>
     <t>Record</t>
   </si>
@@ -33,202 +33,175 @@
     <t>Robbie's Rowdy Team</t>
   </si>
   <si>
+    <t>Maulin's Monstrous Team</t>
+  </si>
+  <si>
+    <t>BB-Ate My Lemons</t>
+  </si>
+  <si>
     <t>Alley Cats</t>
   </si>
   <si>
-    <t>Maulin's Monstrous Team</t>
+    <t>The Turbanator</t>
+  </si>
+  <si>
+    <t>LaPortAuthority</t>
+  </si>
+  <si>
+    <t>Cutlet Slutz</t>
   </si>
   <si>
     <t>Potato Squad</t>
   </si>
   <si>
-    <t>BB-Ate My Lemons</t>
-  </si>
-  <si>
-    <t>The Turbanator</t>
-  </si>
-  <si>
-    <t>Cutlet Slutz</t>
+    <t>Knee Chubbs</t>
   </si>
   <si>
     <t>J.K. Dobby</t>
   </si>
   <si>
-    <t>LaPortAuthority</t>
-  </si>
-  <si>
-    <t>Knee Chubbs</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>99.7%</t>
-  </si>
-  <si>
-    <t>96.2%</t>
-  </si>
-  <si>
-    <t>88.7%</t>
-  </si>
-  <si>
-    <t>87.3%</t>
-  </si>
-  <si>
-    <t>81.6%</t>
-  </si>
-  <si>
-    <t>63.4%</t>
-  </si>
-  <si>
-    <t>29.9%</t>
-  </si>
-  <si>
-    <t>21.7%</t>
-  </si>
-  <si>
-    <t>21.2%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>-33233</t>
-  </si>
-  <si>
-    <t>-2532</t>
-  </si>
-  <si>
-    <t>-785</t>
-  </si>
-  <si>
-    <t>-687</t>
-  </si>
-  <si>
-    <t>-443</t>
-  </si>
-  <si>
-    <t>-173</t>
-  </si>
-  <si>
-    <t>+234</t>
-  </si>
-  <si>
-    <t>+361</t>
-  </si>
-  <si>
-    <t>+372</t>
-  </si>
-  <si>
-    <t>+871</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>98.3%</t>
+  </si>
+  <si>
+    <t>94.3%</t>
+  </si>
+  <si>
+    <t>93.8%</t>
+  </si>
+  <si>
+    <t>72.1%</t>
+  </si>
+  <si>
+    <t>53.1%</t>
+  </si>
+  <si>
+    <t>41.3%</t>
+  </si>
+  <si>
+    <t>37.3%</t>
+  </si>
+  <si>
+    <t>5.5%</t>
+  </si>
+  <si>
+    <t>4.4%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-5782</t>
+  </si>
+  <si>
+    <t>-1654</t>
+  </si>
+  <si>
+    <t>-1513</t>
+  </si>
+  <si>
+    <t>-258</t>
+  </si>
+  <si>
+    <t>-113</t>
+  </si>
+  <si>
+    <t>+142</t>
+  </si>
+  <si>
+    <t>+168</t>
+  </si>
+  <si>
+    <t>+1718</t>
+  </si>
+  <si>
+    <t>+2173</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>67.0%</t>
-  </si>
-  <si>
-    <t>16.4%</t>
-  </si>
-  <si>
-    <t>7.2%</t>
+    <t>72.3%</t>
+  </si>
+  <si>
+    <t>14.2%</t>
+  </si>
+  <si>
+    <t>6.6%</t>
+  </si>
+  <si>
+    <t>5.7%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-261</t>
+  </si>
+  <si>
+    <t>+604</t>
+  </si>
+  <si>
+    <t>+1415</t>
+  </si>
+  <si>
+    <t>+1654</t>
+  </si>
+  <si>
+    <t>+9900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>50.2%</t>
+  </si>
+  <si>
+    <t>35.2%</t>
   </si>
   <si>
     <t>4.8%</t>
   </si>
   <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-203</t>
-  </si>
-  <si>
-    <t>+510</t>
-  </si>
-  <si>
-    <t>+1289</t>
+    <t>3.2%</t>
+  </si>
+  <si>
+    <t>0.9%</t>
+  </si>
+  <si>
+    <t>-101</t>
+  </si>
+  <si>
+    <t>+184</t>
   </si>
   <si>
     <t>+1983</t>
   </si>
   <si>
-    <t>+2930</t>
-  </si>
-  <si>
-    <t>+9900</t>
-  </si>
-  <si>
-    <t>+49900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>38.8%</t>
-  </si>
-  <si>
-    <t>21.0%</t>
-  </si>
-  <si>
-    <t>20.3%</t>
-  </si>
-  <si>
-    <t>14.4%</t>
-  </si>
-  <si>
-    <t>2.9%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>+158</t>
-  </si>
-  <si>
-    <t>+376</t>
-  </si>
-  <si>
-    <t>+393</t>
-  </si>
-  <si>
-    <t>+594</t>
-  </si>
-  <si>
-    <t>+3348</t>
-  </si>
-  <si>
-    <t>+6567</t>
-  </si>
-  <si>
-    <t>+16567</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>+3025</t>
+  </si>
+  <si>
+    <t>+11011</t>
   </si>
 </sst>
 </file>
@@ -611,10 +584,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -622,13 +595,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -636,13 +609,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -653,10 +626,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -664,13 +637,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -678,13 +651,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -692,13 +665,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -706,13 +679,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -720,13 +693,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -737,10 +710,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -761,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -775,10 +748,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -786,13 +759,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -800,13 +773,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -817,10 +790,10 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -828,55 +801,55 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -884,13 +857,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -901,10 +874,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -939,38 +912,38 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -978,13 +951,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -992,13 +965,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1006,55 +979,55 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1065,10 +1038,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Campers and Skiers and Prahlad 2026 Betting Odds.xlsx
+++ b/data/odds/Campers and Skiers and Prahlad 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="69">
   <si>
     <t>Record</t>
   </si>
@@ -36,118 +36,127 @@
     <t>Maulin's Monstrous Team</t>
   </si>
   <si>
+    <t>Alley Cats</t>
+  </si>
+  <si>
+    <t>The Turbanator</t>
+  </si>
+  <si>
+    <t>Cutlet Slutz</t>
+  </si>
+  <si>
     <t>BB-Ate My Lemons</t>
   </si>
   <si>
-    <t>Alley Cats</t>
-  </si>
-  <si>
-    <t>The Turbanator</t>
-  </si>
-  <si>
     <t>LaPortAuthority</t>
   </si>
   <si>
-    <t>Cutlet Slutz</t>
-  </si>
-  <si>
     <t>Potato Squad</t>
   </si>
   <si>
+    <t>J.K. Dobby</t>
+  </si>
+  <si>
     <t>Knee Chubbs</t>
   </si>
   <si>
-    <t>J.K. Dobby</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
   </si>
   <si>
     <t>99.9%</t>
   </si>
   <si>
-    <t>98.3%</t>
-  </si>
-  <si>
-    <t>94.3%</t>
-  </si>
-  <si>
-    <t>93.8%</t>
-  </si>
-  <si>
-    <t>72.1%</t>
-  </si>
-  <si>
-    <t>53.1%</t>
-  </si>
-  <si>
-    <t>41.3%</t>
-  </si>
-  <si>
-    <t>37.3%</t>
-  </si>
-  <si>
-    <t>5.5%</t>
-  </si>
-  <si>
-    <t>4.4%</t>
+    <t>97.4%</t>
+  </si>
+  <si>
+    <t>93.7%</t>
+  </si>
+  <si>
+    <t>91.8%</t>
+  </si>
+  <si>
+    <t>67.7%</t>
+  </si>
+  <si>
+    <t>67.6%</t>
+  </si>
+  <si>
+    <t>30.4%</t>
+  </si>
+  <si>
+    <t>23.8%</t>
+  </si>
+  <si>
+    <t>20.2%</t>
+  </si>
+  <si>
+    <t>7.5%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-5782</t>
-  </si>
-  <si>
-    <t>-1654</t>
-  </si>
-  <si>
-    <t>-1513</t>
-  </si>
-  <si>
-    <t>-258</t>
-  </si>
-  <si>
-    <t>-113</t>
-  </si>
-  <si>
-    <t>+142</t>
-  </si>
-  <si>
-    <t>+168</t>
-  </si>
-  <si>
-    <t>+1718</t>
-  </si>
-  <si>
-    <t>+2173</t>
+    <t>-3746</t>
+  </si>
+  <si>
+    <t>-1487</t>
+  </si>
+  <si>
+    <t>-1120</t>
+  </si>
+  <si>
+    <t>-210</t>
+  </si>
+  <si>
+    <t>-209</t>
+  </si>
+  <si>
+    <t>+229</t>
+  </si>
+  <si>
+    <t>+320</t>
+  </si>
+  <si>
+    <t>+395</t>
+  </si>
+  <si>
+    <t>+1233</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>72.3%</t>
-  </si>
-  <si>
-    <t>14.2%</t>
-  </si>
-  <si>
-    <t>6.6%</t>
-  </si>
-  <si>
-    <t>5.7%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
+    <t>75.3%</t>
+  </si>
+  <si>
+    <t>10.7%</t>
+  </si>
+  <si>
+    <t>7.0%</t>
+  </si>
+  <si>
+    <t>5.3%</t>
+  </si>
+  <si>
+    <t>0.9%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
   </si>
   <si>
     <t>0.1%</t>
@@ -156,52 +165,64 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-261</t>
-  </si>
-  <si>
-    <t>+604</t>
-  </si>
-  <si>
-    <t>+1415</t>
-  </si>
-  <si>
-    <t>+1654</t>
-  </si>
-  <si>
-    <t>+9900</t>
+    <t>-305</t>
+  </si>
+  <si>
+    <t>+835</t>
+  </si>
+  <si>
+    <t>+1329</t>
+  </si>
+  <si>
+    <t>+1787</t>
+  </si>
+  <si>
+    <t>+11011</t>
+  </si>
+  <si>
+    <t>+19900</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>50.2%</t>
-  </si>
-  <si>
-    <t>35.2%</t>
-  </si>
-  <si>
-    <t>4.8%</t>
-  </si>
-  <si>
-    <t>3.2%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
-  </si>
-  <si>
-    <t>-101</t>
-  </si>
-  <si>
-    <t>+184</t>
-  </si>
-  <si>
-    <t>+1983</t>
-  </si>
-  <si>
-    <t>+3025</t>
-  </si>
-  <si>
-    <t>+11011</t>
+    <t>47.1%</t>
+  </si>
+  <si>
+    <t>18.4%</t>
+  </si>
+  <si>
+    <t>15.3%</t>
+  </si>
+  <si>
+    <t>14.3%</t>
+  </si>
+  <si>
+    <t>2.5%</t>
+  </si>
+  <si>
+    <t>2.3%</t>
+  </si>
+  <si>
+    <t>+112</t>
+  </si>
+  <si>
+    <t>+443</t>
+  </si>
+  <si>
+    <t>+554</t>
+  </si>
+  <si>
+    <t>+599</t>
+  </si>
+  <si>
+    <t>+3900</t>
+  </si>
+  <si>
+    <t>+4248</t>
   </si>
 </sst>
 </file>
@@ -584,10 +605,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -595,13 +616,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -612,10 +633,10 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -623,13 +644,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -640,10 +661,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -654,10 +675,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -665,13 +686,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -679,13 +700,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -693,13 +714,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -707,13 +728,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +755,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -748,10 +769,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -759,13 +780,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -776,10 +797,10 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -787,13 +808,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -804,66 +825,66 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -871,13 +892,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -898,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -909,13 +930,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -923,97 +944,97 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1024,10 +1045,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1038,10 +1059,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Campers and Skiers and Prahlad 2026 Betting Odds.xlsx
+++ b/data/odds/Campers and Skiers and Prahlad 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
   <si>
     <t>Record</t>
   </si>
@@ -33,196 +33,193 @@
     <t>Robbie's Rowdy Team</t>
   </si>
   <si>
+    <t>Alley Cats</t>
+  </si>
+  <si>
+    <t>Cutlet Slutz</t>
+  </si>
+  <si>
+    <t>The Turbanator</t>
+  </si>
+  <si>
     <t>Maulin's Monstrous Team</t>
   </si>
   <si>
-    <t>Alley Cats</t>
-  </si>
-  <si>
-    <t>The Turbanator</t>
-  </si>
-  <si>
-    <t>Cutlet Slutz</t>
-  </si>
-  <si>
     <t>BB-Ate My Lemons</t>
   </si>
   <si>
     <t>LaPortAuthority</t>
   </si>
   <si>
+    <t>J.K. Dobby</t>
+  </si>
+  <si>
     <t>Potato Squad</t>
   </si>
   <si>
-    <t>J.K. Dobby</t>
-  </si>
-  <si>
     <t>Knee Chubbs</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>97.4%</t>
-  </si>
-  <si>
-    <t>93.7%</t>
-  </si>
-  <si>
-    <t>91.8%</t>
-  </si>
-  <si>
-    <t>67.7%</t>
-  </si>
-  <si>
-    <t>67.6%</t>
-  </si>
-  <si>
-    <t>30.4%</t>
-  </si>
-  <si>
-    <t>23.8%</t>
-  </si>
-  <si>
-    <t>20.2%</t>
-  </si>
-  <si>
-    <t>7.5%</t>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>95.5%</t>
+  </si>
+  <si>
+    <t>91.2%</t>
+  </si>
+  <si>
+    <t>85.6%</t>
+  </si>
+  <si>
+    <t>83.9%</t>
+  </si>
+  <si>
+    <t>77.8%</t>
+  </si>
+  <si>
+    <t>42.8%</t>
+  </si>
+  <si>
+    <t>11.8%</t>
+  </si>
+  <si>
+    <t>9.0%</t>
+  </si>
+  <si>
+    <t>2.4%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-3746</t>
-  </si>
-  <si>
-    <t>-1487</t>
-  </si>
-  <si>
-    <t>-1120</t>
-  </si>
-  <si>
-    <t>-210</t>
-  </si>
-  <si>
-    <t>-209</t>
-  </si>
-  <si>
-    <t>+229</t>
-  </si>
-  <si>
-    <t>+320</t>
-  </si>
-  <si>
-    <t>+395</t>
-  </si>
-  <si>
-    <t>+1233</t>
+    <t>-2122</t>
+  </si>
+  <si>
+    <t>-1036</t>
+  </si>
+  <si>
+    <t>-594</t>
+  </si>
+  <si>
+    <t>-521</t>
+  </si>
+  <si>
+    <t>-350</t>
+  </si>
+  <si>
+    <t>+134</t>
+  </si>
+  <si>
+    <t>+747</t>
+  </si>
+  <si>
+    <t>+1011</t>
+  </si>
+  <si>
+    <t>+4067</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>75.3%</t>
-  </si>
-  <si>
-    <t>10.7%</t>
-  </si>
-  <si>
-    <t>7.0%</t>
-  </si>
-  <si>
-    <t>5.3%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
+    <t>91.5%</t>
+  </si>
+  <si>
+    <t>3.8%</t>
+  </si>
+  <si>
+    <t>2.6%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>0.2%</t>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-1076</t>
+  </si>
+  <si>
+    <t>+2532</t>
+  </si>
+  <si>
+    <t>+3746</t>
+  </si>
+  <si>
+    <t>+9900</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>+19900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>56.2%</t>
+  </si>
+  <si>
+    <t>19.4%</t>
+  </si>
+  <si>
+    <t>19.2%</t>
+  </si>
+  <si>
+    <t>4.4%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-305</t>
-  </si>
-  <si>
-    <t>+835</t>
-  </si>
-  <si>
-    <t>+1329</t>
-  </si>
-  <si>
-    <t>+1787</t>
-  </si>
-  <si>
-    <t>+11011</t>
-  </si>
-  <si>
-    <t>+19900</t>
-  </si>
-  <si>
-    <t>+49900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>47.1%</t>
-  </si>
-  <si>
-    <t>18.4%</t>
-  </si>
-  <si>
-    <t>15.3%</t>
-  </si>
-  <si>
-    <t>14.3%</t>
-  </si>
-  <si>
-    <t>2.5%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
-  </si>
-  <si>
-    <t>+112</t>
-  </si>
-  <si>
-    <t>+443</t>
-  </si>
-  <si>
-    <t>+554</t>
-  </si>
-  <si>
-    <t>+599</t>
-  </si>
-  <si>
-    <t>+3900</t>
-  </si>
-  <si>
-    <t>+4248</t>
+    <t>-128</t>
+  </si>
+  <si>
+    <t>+415</t>
+  </si>
+  <si>
+    <t>+421</t>
+  </si>
+  <si>
+    <t>+2173</t>
+  </si>
+  <si>
+    <t>+24900</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
 </sst>
 </file>
@@ -605,10 +602,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -619,10 +616,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -630,13 +627,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -644,13 +641,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -661,10 +658,10 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -675,10 +672,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -689,10 +686,10 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -703,10 +700,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -714,13 +711,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -728,13 +725,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -755,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -769,10 +766,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -783,10 +780,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -794,41 +791,41 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -839,66 +836,66 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -919,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -930,83 +927,83 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1014,41 +1011,41 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1059,10 +1056,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Campers and Skiers and Prahlad 2026 Betting Odds.xlsx
+++ b/data/odds/Campers and Skiers and Prahlad 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="63">
   <si>
     <t>Record</t>
   </si>
@@ -81,76 +81,70 @@
     <t>100.0%</t>
   </si>
   <si>
-    <t>95.5%</t>
-  </si>
-  <si>
-    <t>91.2%</t>
-  </si>
-  <si>
-    <t>85.6%</t>
-  </si>
-  <si>
-    <t>83.9%</t>
-  </si>
-  <si>
-    <t>77.8%</t>
-  </si>
-  <si>
-    <t>42.8%</t>
-  </si>
-  <si>
-    <t>11.8%</t>
-  </si>
-  <si>
-    <t>9.0%</t>
-  </si>
-  <si>
-    <t>2.4%</t>
+    <t>97.1%</t>
+  </si>
+  <si>
+    <t>92.2%</t>
+  </si>
+  <si>
+    <t>85.9%</t>
+  </si>
+  <si>
+    <t>83.0%</t>
+  </si>
+  <si>
+    <t>77.1%</t>
+  </si>
+  <si>
+    <t>38.8%</t>
+  </si>
+  <si>
+    <t>14.7%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>2.6%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-2122</t>
-  </si>
-  <si>
-    <t>-1036</t>
-  </si>
-  <si>
-    <t>-594</t>
-  </si>
-  <si>
-    <t>-521</t>
-  </si>
-  <si>
-    <t>-350</t>
-  </si>
-  <si>
-    <t>+134</t>
-  </si>
-  <si>
-    <t>+747</t>
-  </si>
-  <si>
-    <t>+1011</t>
-  </si>
-  <si>
-    <t>+4067</t>
+    <t>-3348</t>
+  </si>
+  <si>
+    <t>-1182</t>
+  </si>
+  <si>
+    <t>-609</t>
+  </si>
+  <si>
+    <t>-488</t>
+  </si>
+  <si>
+    <t>-337</t>
+  </si>
+  <si>
+    <t>+158</t>
+  </si>
+  <si>
+    <t>+580</t>
+  </si>
+  <si>
+    <t>+1063</t>
+  </si>
+  <si>
+    <t>+3746</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>91.5%</t>
-  </si>
-  <si>
-    <t>3.8%</t>
-  </si>
-  <si>
-    <t>2.6%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
+    <t>5.0%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
   </si>
   <si>
     <t>0.6%</t>
@@ -162,16 +156,10 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-1076</t>
-  </si>
-  <si>
-    <t>+2532</t>
-  </si>
-  <si>
-    <t>+3746</t>
-  </si>
-  <si>
-    <t>+9900</t>
+    <t>+1900</t>
+  </si>
+  <si>
+    <t>+8991</t>
   </si>
   <si>
     <t>+16567</t>
@@ -183,43 +171,40 @@
     <t>+99900</t>
   </si>
   <si>
-    <t>56.2%</t>
-  </si>
-  <si>
-    <t>19.4%</t>
-  </si>
-  <si>
-    <t>19.2%</t>
-  </si>
-  <si>
-    <t>4.4%</t>
+    <t>52.0%</t>
+  </si>
+  <si>
+    <t>25.0%</t>
+  </si>
+  <si>
+    <t>16.2%</t>
+  </si>
+  <si>
+    <t>5.5%</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>-128</t>
-  </si>
-  <si>
-    <t>+415</t>
-  </si>
-  <si>
-    <t>+421</t>
-  </si>
-  <si>
-    <t>+2173</t>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>-108</t>
+  </si>
+  <si>
+    <t>+300</t>
+  </si>
+  <si>
+    <t>+517</t>
+  </si>
+  <si>
+    <t>+1718</t>
   </si>
   <si>
     <t>+24900</t>
   </si>
   <si>
-    <t>+33233</t>
+    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -766,10 +751,10 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -780,10 +765,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -794,10 +779,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -808,10 +793,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -822,10 +807,10 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -836,10 +821,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -850,10 +835,10 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -864,10 +849,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -878,10 +863,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -892,10 +877,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -930,38 +915,38 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -972,66 +957,66 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1042,10 +1027,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1056,10 +1041,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
